--- a/data/trans_camb/IP2002-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Edad-trans_camb.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,09</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,25</t>
+          <t>-1,06; 3,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,24</t>
+          <t>-1,1; 3,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,08</t>
+          <t>-0,51; 4,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,35</t>
+          <t>0,25; 5,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,64</t>
+          <t>-2,69; 0,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,61</t>
+          <t>-0,44; 5,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,61</t>
+          <t>0,45; 3,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,22</t>
+          <t>-1,26; 1,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,35</t>
+          <t>0,31; 4,54</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 583,9</t>
+          <t>-58,72; 584,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,91; 550,76</t>
+          <t>-62,18; 771,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 738,88</t>
+          <t>-33,82; 791,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 682,29</t>
+          <t>-12,07; 641,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 855,09</t>
+          <t>-31,23; 669,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 372,8</t>
+          <t>12,91; 365,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,54; 136,35</t>
+          <t>-61,37; 142,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 433,4</t>
+          <t>6,77; 405,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 2,4</t>
+          <t>-8,6; 3,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 3,74</t>
+          <t>-7,24; 4,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 2,9</t>
+          <t>-8,7; 3,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 3,12</t>
+          <t>-10,23; 3,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,96; -1,36</t>
+          <t>-12,84; -1,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,3; -4,05</t>
+          <t>-15,32; -4,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 0,79</t>
+          <t>-7,79; 0,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,48; -0,32</t>
+          <t>-8,54; -0,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,43; -2,25</t>
+          <t>-10,41; -2,6</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 28,47</t>
+          <t>-57,84; 39,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 42,75</t>
+          <t>-47,76; 52,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 34,43</t>
+          <t>-56,25; 46,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,65; 32,49</t>
+          <t>-56,52; 30,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,56; -11,97</t>
+          <t>-72,24; -13,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,7; -29,18</t>
+          <t>-82,3; -35,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 6,63</t>
+          <t>-48,89; 8,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,86; -2,26</t>
+          <t>-53,81; -0,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,1; -19,38</t>
+          <t>-65,58; -23,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 1,99</t>
+          <t>-9,31; 2,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 1,19</t>
+          <t>-9,99; 1,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,65; -2,7</t>
+          <t>-12,24; -3,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 4,38</t>
+          <t>-6,0; 4,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 3,72</t>
+          <t>-7,05; 3,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,55; -1,37</t>
+          <t>-10,78; -1,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1,52</t>
+          <t>-6,33; 1,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 0,63</t>
+          <t>-7,12; 0,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -3,2</t>
+          <t>-10,21; -3,31</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 19,19</t>
+          <t>-56,05; 18,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 12,34</t>
+          <t>-59,67; 10,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,66; -21,73</t>
+          <t>-73,77; -24,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,56; 45,98</t>
+          <t>-43,2; 44,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 39,67</t>
+          <t>-49,16; 39,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,4; -13,0</t>
+          <t>-70,99; -13,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 12,24</t>
+          <t>-41,88; 15,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 5,68</t>
+          <t>-46,61; 9,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,7; -28,54</t>
+          <t>-66,79; -28,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,76</t>
+          <t>-3,96; 0,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,29</t>
+          <t>-3,2; 1,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,11</t>
+          <t>-3,52; 1,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,86</t>
+          <t>-2,59; 1,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,19</t>
+          <t>-4,44; -0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,15</t>
+          <t>-4,5; -0,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,66</t>
+          <t>-2,46; 0,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,23</t>
+          <t>-3,19; -0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,11</t>
+          <t>-3,38; -0,18</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 13,39</t>
+          <t>-47,71; 7,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 21,72</t>
+          <t>-36,57; 27,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,44; 17,79</t>
+          <t>-41,86; 19,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 32,18</t>
+          <t>-31,11; 29,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,09; -2,18</t>
+          <t>-52,49; -2,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 3,16</t>
+          <t>-53,73; -2,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,82; 10,09</t>
+          <t>-30,91; 10,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,37; -3,14</t>
+          <t>-40,41; 0,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -1,49</t>
+          <t>-41,82; -2,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Edad-trans_camb.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 7,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,2</t>
+          <t>-0,93; 3,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,18</t>
+          <t>-0,99; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,79</t>
+          <t>-0,3; 5,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,4</t>
+          <t>0,31; 5,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,68</t>
+          <t>-2,66; 0,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,59</t>
+          <t>-0,39; 5,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,59</t>
+          <t>0,26; 3,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,29</t>
+          <t>-1,31; 1,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,54</t>
+          <t>0,31; 4,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,72; 584,5</t>
+          <t>-57,3; 565,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,18; 771,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 791,64</t>
+          <t>-35,71; 817,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 641,49</t>
+          <t>-5,76; 696,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 134,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,23; 669,55</t>
+          <t>-31,68; 676,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,91; 365,02</t>
+          <t>4,99; 407,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 142,42</t>
+          <t>-62,25; 155,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 405,83</t>
+          <t>6,62; 454,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 3,08</t>
+          <t>-8,86; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 4,38</t>
+          <t>-7,14; 4,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 3,57</t>
+          <t>-8,66; 3,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 3,1</t>
+          <t>-10,01; 2,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,84; -1,79</t>
+          <t>-12,87; -1,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,32; -4,44</t>
+          <t>-15,51; -4,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 0,9</t>
+          <t>-7,84; 0,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -0,11</t>
+          <t>-8,6; -0,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -2,6</t>
+          <t>-10,78; -2,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,84; 39,7</t>
+          <t>-58,41; 37,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 52,92</t>
+          <t>-45,86; 54,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,25; 46,23</t>
+          <t>-58,09; 37,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 30,21</t>
+          <t>-54,52; 26,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,24; -13,98</t>
+          <t>-70,86; -12,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,3; -35,49</t>
+          <t>-82,19; -35,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,89; 8,63</t>
+          <t>-49,68; 4,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,81; -0,58</t>
+          <t>-54,3; -5,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,58; -23,02</t>
+          <t>-66,39; -24,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 2,02</t>
+          <t>-9,55; 1,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 1,01</t>
+          <t>-9,91; 0,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -3,09</t>
+          <t>-12,54; -2,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 4,26</t>
+          <t>-5,97; 4,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 3,79</t>
+          <t>-7,27; 4,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -1,6</t>
+          <t>-10,77; -1,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 1,5</t>
+          <t>-5,98; 1,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 0,99</t>
+          <t>-6,91; 0,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -3,31</t>
+          <t>-9,94; -3,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,05; 18,89</t>
+          <t>-57,33; 12,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,67; 10,67</t>
+          <t>-59,68; 5,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,77; -24,8</t>
+          <t>-74,08; -24,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,2; 44,04</t>
+          <t>-40,79; 43,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 39,61</t>
+          <t>-49,57; 43,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,99; -13,58</t>
+          <t>-69,88; -14,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 15,34</t>
+          <t>-42,38; 10,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 9,6</t>
+          <t>-47,56; 6,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,79; -28,13</t>
+          <t>-66,76; -28,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,49</t>
+          <t>-3,85; 0,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,5</t>
+          <t>-3,12; 1,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,11</t>
+          <t>-3,55; 0,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,92</t>
+          <t>-2,55; 1,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; -0,26</t>
+          <t>-4,59; -0,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,21</t>
+          <t>-4,43; -0,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,66</t>
+          <t>-2,59; 0,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,0</t>
+          <t>-3,21; -0,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,18</t>
+          <t>-3,4; -0,18</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 7,83</t>
+          <t>-46,26; 9,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 27,92</t>
+          <t>-38,22; 23,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 19,28</t>
+          <t>-43,62; 16,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 29,8</t>
+          <t>-30,37; 30,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,49; -2,5</t>
+          <t>-53,54; -5,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -2,18</t>
+          <t>-53,64; 0,07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 10,48</t>
+          <t>-32,53; 9,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 0,01</t>
+          <t>-39,69; -0,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -2,1</t>
+          <t>-42,41; -2,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2002-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2002-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -634,24 +634,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>1,42</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -687,24 +687,24 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,74</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,38</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,24</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,07</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,59</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>2,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,39</t>
+          <t>0,25; 5,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,34</t>
+          <t>-2,63; 0,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,14</t>
+          <t>-0,29; 5,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,08</t>
+          <t>-0,94; 3,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,64</t>
+          <t>-0,99; 3,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,48</t>
+          <t>-0,1; 5,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,62</t>
+          <t>0,2; 3,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,29</t>
+          <t>-1,27; 1,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,26</t>
+          <t>0,37; 4,65</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>159,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-50,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>138,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>75,49%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>59,21%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>135,68%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>159,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-50,04%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>134,03%</t>
+          <t>157,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>135,75%</t>
+          <t>147,39%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,3; 565,77</t>
+          <t>-2,7; 682,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,71; 817,63</t>
+          <t>-31,11; 870,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 696,86</t>
+          <t>-49,62; 583,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,77</t>
+          <t>-59,91; 550,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 676,55</t>
+          <t>-37,36; 788,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 407,33</t>
+          <t>3,76; 372,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,25; 155,51</t>
+          <t>-61,54; 136,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 454,24</t>
+          <t>7,67; 459,23</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-7,33</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-9,7</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,43</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,66</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,33</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,52</t>
+          <t>-2,59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,37</t>
+          <t>-6,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 2,69</t>
+          <t>-9,87; 3,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 4,62</t>
+          <t>-12,96; -1,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 3,11</t>
+          <t>-15,48; -4,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 2,61</t>
+          <t>-9,3; 2,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -1,7</t>
+          <t>-7,79; 3,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,51; -4,2</t>
+          <t>-8,66; 2,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 0,47</t>
+          <t>-8,21; 0,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -0,73</t>
+          <t>-8,48; -0,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -2,92</t>
+          <t>-10,38; -2,2</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-24,2%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-50,62%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-66,96%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-26,62%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-12,02%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-22,33%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-24,2%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-50,62%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-65,73%</t>
+          <t>-21,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-48,09%</t>
+          <t>-48,02%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 37,88</t>
+          <t>-54,65; 32,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,86; 54,87</t>
+          <t>-72,56; -11,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,09; 37,43</t>
+          <t>-83,34; -31,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,52; 26,02</t>
+          <t>-59,49; 28,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,86; -12,13</t>
+          <t>-50,09; 42,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,19; -35,94</t>
+          <t>-57,41; 33,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 4,85</t>
+          <t>-51,33; 6,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,3; -5,79</t>
+          <t>-54,86; -2,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,39; -24,91</t>
+          <t>-66,14; -19,71</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,89</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,13</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-3,94</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,43</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,58</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,89</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,97</t>
+          <t>-7,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,75</t>
+          <t>-6,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 1,41</t>
+          <t>-5,95; 4,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 0,51</t>
+          <t>-7,06; 3,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,54; -2,78</t>
+          <t>-10,64; -1,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 4,25</t>
+          <t>-9,03; 1,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 4,16</t>
+          <t>-9,37; 1,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -1,86</t>
+          <t>-12,37; -2,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 1,2</t>
+          <t>-5,99; 1,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 0,69</t>
+          <t>-6,68; 0,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -3,44</t>
+          <t>-10,09; -3,4</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-9,55%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-15,33%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-49,77%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-28,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-31,77%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-54,35%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-9,55%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-15,33%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-48,48%</t>
+          <t>-53,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-51,52%</t>
+          <t>-51,6%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,33; 12,82</t>
+          <t>-41,56; 45,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 5,01</t>
+          <t>-48,31; 39,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,08; -24,08</t>
+          <t>-71,15; -14,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 43,65</t>
+          <t>-54,25; 19,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 43,68</t>
+          <t>-57,59; 12,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,88; -14,17</t>
+          <t>-72,31; -22,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 10,45</t>
+          <t>-40,72; 12,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,56; 6,15</t>
+          <t>-46,2; 5,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,76; -28,54</t>
+          <t>-66,6; -29,44</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,35</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,47</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-2,31</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,89</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-1,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,52</t>
+          <t>-2,62; 1,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,38</t>
+          <t>-4,54; -0,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,99</t>
+          <t>-4,32; 0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,92</t>
+          <t>-3,76; 0,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -0,35</t>
+          <t>-3,15; 1,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -0,03</t>
+          <t>-3,29; 1,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,65</t>
+          <t>-2,57; 0,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,07</t>
+          <t>-3,23; -0,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,4; -0,18</t>
+          <t>-3,25; -0,03</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-4,85%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-33,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-31,66%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-22,12%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-12,54%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-16,64%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-4,85%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-33,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,07%</t>
+          <t>-13,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,38%</t>
+          <t>-23,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 9,04</t>
+          <t>-31,7; 32,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 23,18</t>
+          <t>-54,09; -2,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 16,33</t>
+          <t>-52,1; 1,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 30,76</t>
+          <t>-45,78; 13,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-53,54; -5,19</t>
+          <t>-39,31; 21,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 0,07</t>
+          <t>-39,33; 23,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 9,75</t>
+          <t>-31,82; 10,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,69; -0,41</t>
+          <t>-40,37; -3,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -2,52</t>
+          <t>-40,37; 0,26</t>
         </is>
       </c>
     </row>
